--- a/SGC-CKN/Excel/c5a2837e-6ddd-420e-97c5-b885217dfadd_Phường_Hạc_Thành__tỉnh_Thanh_Hoá_P11-3_D800_19-03-2026.xlsx
+++ b/SGC-CKN/Excel/c5a2837e-6ddd-420e-97c5-b885217dfadd_Phường_Hạc_Thành__tỉnh_Thanh_Hoá_P11-3_D800_19-03-2026.xlsx
@@ -35,7 +35,7 @@
     <t>Số hiệu cọc</t>
   </si>
   <si>
-    <t>P11-3</t>
+    <t>P11-03</t>
   </si>
   <si>
     <t>Biên bản số</t>

--- a/SGC-CKN/Excel/c5a2837e-6ddd-420e-97c5-b885217dfadd_Phường_Hạc_Thành__tỉnh_Thanh_Hoá_P11-3_D800_19-03-2026.xlsx
+++ b/SGC-CKN/Excel/c5a2837e-6ddd-420e-97c5-b885217dfadd_Phường_Hạc_Thành__tỉnh_Thanh_Hoá_P11-3_D800_19-03-2026.xlsx
@@ -12,12 +12,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="63">
   <si>
     <t>Dự án</t>
   </si>
   <si>
-    <t>Dự án số 1 khu đô thị trung tâm thành phố Thanh Hóa (Vinhomes Star City)</t>
+    <t>Star City Thanh Hóa</t>
   </si>
   <si>
     <t>Hạng mục</t>
@@ -38,10 +38,10 @@
     <t>P11-03</t>
   </si>
   <si>
-    <t>Biên bản số</t>
-  </si>
-  <si>
-    <t>PA1-5</t>
+    <t>Tên Máy khoan</t>
+  </si>
+  <si>
+    <t/>
   </si>
   <si>
     <t>Đường kính</t>
@@ -95,7 +95,7 @@
     <t>2</t>
   </si>
   <si>
-    <t>Sét pha, xám nâu, TT dẻo mềm</t>
+    <t>Sét pha màu xám xanh, xám đen, xám nâu, xám ghi, TT dẻo mềm</t>
   </si>
   <si>
     <t xml:space="preserve">07:50
@@ -106,9 +106,6 @@
 19/03/2026</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
     <t>3</t>
   </si>
   <si>
@@ -122,7 +119,7 @@
     <t>7</t>
   </si>
   <si>
-    <t>Sét- đối chỗ kẹp cát pha, lẫn dăm sạn TT dẻo mềm</t>
+    <t>Sét, đôi chỗ kẹp cát pha, lẫn dăm sạn TT dẻo mềm</t>
   </si>
   <si>
     <t xml:space="preserve">08:45
@@ -152,7 +149,7 @@
     <t>13</t>
   </si>
   <si>
-    <t>Cát pha, xám vàng, xám ghi TT dẻo</t>
+    <t>Cát pha xám ghi, xám nâu, xám vàng TT dẻo</t>
   </si>
   <si>
     <t xml:space="preserve">11:10
@@ -162,7 +159,7 @@
     <t>14</t>
   </si>
   <si>
-    <t>Cát thô vừa, KC chặt vừa lẫn sỏi sạn, có chỗ là hạt cát nhỏ, bụi</t>
+    <t>Cát thô vừa, xám vàng, xám xanh TT chặt lẫn sỏi sạn, có chỗ là cát hạt nhỏ, bụi</t>
   </si>
   <si>
     <t xml:space="preserve">11:40
@@ -175,7 +172,7 @@
     <t>16</t>
   </si>
   <si>
-    <t>Sỏi xám vàng, xám xanh TT rất chặt</t>
+    <t>Sỏi xám vàng, nâu vàng, xám xanh TT rất chặt</t>
   </si>
   <si>
     <t xml:space="preserve">12:11
@@ -1166,24 +1163,24 @@
         <v>5.4</v>
       </c>
       <c r="K11" s="6" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B12" s="9" t="s">
         <v>11</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D12" s="11" t="s">
         <v>29</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F12" s="9">
         <v>-2.18</v>
@@ -1201,24 +1198,24 @@
         <v>40.8</v>
       </c>
       <c r="K12" s="10" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B13" s="12" t="s">
         <v>11</v>
       </c>
       <c r="C13" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="D13" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="E13" s="14" t="s">
         <v>35</v>
-      </c>
-      <c r="D13" s="14" t="s">
-        <v>33</v>
-      </c>
-      <c r="E13" s="14" t="s">
-        <v>36</v>
       </c>
       <c r="F13" s="12">
         <v>-12.379999999999999</v>
@@ -1236,24 +1233,24 @@
         <v>15.6</v>
       </c>
       <c r="K13" s="13" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="15" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B14" s="15" t="s">
         <v>11</v>
       </c>
       <c r="C14" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="D14" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="E14" s="17" t="s">
         <v>38</v>
-      </c>
-      <c r="D14" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="E14" s="17" t="s">
-        <v>39</v>
       </c>
       <c r="F14" s="15">
         <v>-17.58</v>
@@ -1271,24 +1268,24 @@
         <v>21.4</v>
       </c>
       <c r="K14" s="16" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="18" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B15" s="18" t="s">
         <v>11</v>
       </c>
       <c r="C15" s="19" t="s">
+        <v>40</v>
+      </c>
+      <c r="D15" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="E15" s="20" t="s">
         <v>41</v>
-      </c>
-      <c r="D15" s="20" t="s">
-        <v>39</v>
-      </c>
-      <c r="E15" s="20" t="s">
-        <v>42</v>
       </c>
       <c r="F15" s="18">
         <v>-28.279999999999998</v>
@@ -1306,24 +1303,24 @@
         <v>5.83</v>
       </c>
       <c r="K15" s="19" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="21" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B16" s="21" t="s">
         <v>11</v>
       </c>
       <c r="C16" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="D16" s="23" t="s">
+        <v>41</v>
+      </c>
+      <c r="E16" s="23" t="s">
         <v>44</v>
-      </c>
-      <c r="D16" s="23" t="s">
-        <v>42</v>
-      </c>
-      <c r="E16" s="23" t="s">
-        <v>45</v>
       </c>
       <c r="F16" s="21">
         <v>-35.080000000000005</v>
@@ -1341,24 +1338,24 @@
         <v>3.33</v>
       </c>
       <c r="K16" s="22" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="25" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B17" s="25" t="s">
         <v>11</v>
       </c>
       <c r="C17" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="D17" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="E17" s="27" t="s">
         <v>47</v>
-      </c>
-      <c r="D17" s="27" t="s">
-        <v>45</v>
-      </c>
-      <c r="E17" s="27" t="s">
-        <v>48</v>
       </c>
       <c r="F17" s="25">
         <v>-37.580000000000005</v>
@@ -1376,24 +1373,24 @@
         <v>16.24</v>
       </c>
       <c r="K17" s="26" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="18" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="28" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B18" s="28" t="s">
         <v>11</v>
       </c>
       <c r="C18" s="29" t="s">
+        <v>50</v>
+      </c>
+      <c r="D18" s="30" t="s">
+        <v>47</v>
+      </c>
+      <c r="E18" s="30" t="s">
         <v>51</v>
-      </c>
-      <c r="D18" s="30" t="s">
-        <v>48</v>
-      </c>
-      <c r="E18" s="30" t="s">
-        <v>52</v>
       </c>
       <c r="F18" s="28">
         <v>-45.699999999999996</v>
@@ -1411,12 +1408,12 @@
         <v>8.75</v>
       </c>
       <c r="K18" s="29" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="21" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="31" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B21" s="31"/>
       <c r="C21" s="31"/>
@@ -1522,31 +1519,31 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C1" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>61</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1586,7 +1583,7 @@
         <v>11</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D3" s="9">
         <v>1</v>
@@ -1615,7 +1612,7 @@
         <v>11</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D4" s="12">
         <v>1</v>
@@ -1644,7 +1641,7 @@
         <v>11</v>
       </c>
       <c r="C5" s="16" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D5" s="15">
         <v>1</v>
@@ -1673,7 +1670,7 @@
         <v>11</v>
       </c>
       <c r="C6" s="19" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D6" s="18">
         <v>1</v>
@@ -1702,7 +1699,7 @@
         <v>11</v>
       </c>
       <c r="C7" s="22" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D7" s="21">
         <v>1</v>
@@ -1731,7 +1728,7 @@
         <v>11</v>
       </c>
       <c r="C8" s="26" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D8" s="25">
         <v>1</v>
@@ -1760,7 +1757,7 @@
         <v>11</v>
       </c>
       <c r="C9" s="29" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D9" s="28">
         <v>1</v>
@@ -1783,13 +1780,13 @@
     </row>
     <row r="10" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="32" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B10" s="33" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="C10" s="33" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="D10" s="33">
         <v>8</v>

--- a/SGC-CKN/Excel/c5a2837e-6ddd-420e-97c5-b885217dfadd_Phường_Hạc_Thành__tỉnh_Thanh_Hoá_P11-3_D800_19-03-2026.xlsx
+++ b/SGC-CKN/Excel/c5a2837e-6ddd-420e-97c5-b885217dfadd_Phường_Hạc_Thành__tỉnh_Thanh_Hoá_P11-3_D800_19-03-2026.xlsx
@@ -41,7 +41,7 @@
     <t>Tên Máy khoan</t>
   </si>
   <si>
-    <t/>
+    <t>SGC-KCN0003</t>
   </si>
   <si>
     <t>Đường kính</t>
@@ -95,7 +95,7 @@
     <t>2</t>
   </si>
   <si>
-    <t>Sét pha màu xám xanh, xám đen, xám nâu, xám ghi, TT dẻo mềm</t>
+    <t>Sét pha, xám xanh, xám đen, xám nâu, xám ghi, TT dẻo mềm</t>
   </si>
   <si>
     <t xml:space="preserve">07:50
@@ -106,10 +106,13 @@
 19/03/2026</t>
   </si>
   <si>
+    <t/>
+  </si>
+  <si>
     <t>3</t>
   </si>
   <si>
-    <t>Sét lẫn hữu cơ, xám nâu, xám đen TT dẻo chảy</t>
+    <t>Sét lẫn hữu cơ, xám nâu, xám đen, xám trắng, xám xanh TT dẻo chảy</t>
   </si>
   <si>
     <t xml:space="preserve">08:25
@@ -139,9 +142,6 @@
     <t>12</t>
   </si>
   <si>
-    <t>Sét pha, xám xanh, xám ghi, TT dẻo mềm lẫn hữu cơ, kẹp cát</t>
-  </si>
-  <si>
     <t xml:space="preserve">10:25
 19/03/2026</t>
   </si>
@@ -159,7 +159,7 @@
     <t>14</t>
   </si>
   <si>
-    <t>Cát thô vừa, xám vàng, xám xanh TT chặt lẫn sỏi sạn, có chỗ là cát hạt nhỏ, bụi</t>
+    <t>Cát thô vừa, xám vàng, xám xanh, xám nâu TT chặt</t>
   </si>
   <si>
     <t xml:space="preserve">11:40
@@ -1163,24 +1163,24 @@
         <v>5.4</v>
       </c>
       <c r="K11" s="6" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="12" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B12" s="9" t="s">
         <v>11</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D12" s="11" t="s">
         <v>29</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F12" s="9">
         <v>-2.18</v>
@@ -1198,24 +1198,24 @@
         <v>40.8</v>
       </c>
       <c r="K12" s="10" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="13" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B13" s="12" t="s">
         <v>11</v>
       </c>
       <c r="C13" s="13" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D13" s="14" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E13" s="14" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F13" s="12">
         <v>-12.379999999999999</v>
@@ -1233,24 +1233,24 @@
         <v>15.6</v>
       </c>
       <c r="K13" s="13" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="14" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="15" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B14" s="15" t="s">
         <v>11</v>
       </c>
       <c r="C14" s="16" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D14" s="17" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E14" s="17" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F14" s="15">
         <v>-17.58</v>
@@ -1268,21 +1268,21 @@
         <v>21.4</v>
       </c>
       <c r="K14" s="16" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="15" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="18" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B15" s="18" t="s">
         <v>11</v>
       </c>
       <c r="C15" s="19" t="s">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="D15" s="20" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E15" s="20" t="s">
         <v>41</v>
@@ -1303,7 +1303,7 @@
         <v>5.83</v>
       </c>
       <c r="K15" s="19" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="16" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -1338,7 +1338,7 @@
         <v>3.33</v>
       </c>
       <c r="K16" s="22" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="17" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -1583,7 +1583,7 @@
         <v>11</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D3" s="9">
         <v>1</v>
@@ -1612,7 +1612,7 @@
         <v>11</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D4" s="12">
         <v>1</v>
@@ -1641,7 +1641,7 @@
         <v>11</v>
       </c>
       <c r="C5" s="16" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D5" s="15">
         <v>1</v>
@@ -1670,7 +1670,7 @@
         <v>11</v>
       </c>
       <c r="C6" s="19" t="s">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="D6" s="18">
         <v>1</v>
@@ -1783,10 +1783,10 @@
         <v>62</v>
       </c>
       <c r="B10" s="33" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="C10" s="33" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="D10" s="33">
         <v>8</v>

--- a/SGC-CKN/Excel/c5a2837e-6ddd-420e-97c5-b885217dfadd_Phường_Hạc_Thành__tỉnh_Thanh_Hoá_P11-3_D800_19-03-2026.xlsx
+++ b/SGC-CKN/Excel/c5a2837e-6ddd-420e-97c5-b885217dfadd_Phường_Hạc_Thành__tỉnh_Thanh_Hoá_P11-3_D800_19-03-2026.xlsx
@@ -23,7 +23,7 @@
     <t>Hạng mục</t>
   </si>
   <si>
-    <t>Thi công cọc khoan nhồi đại trà_lô đất ký hiệu CT-02</t>
+    <t>Thi công cọc khoan nhồi, tường vây cho các hạng mục_Lô CT-02</t>
   </si>
   <si>
     <t>Tên bộ phận</t>
@@ -122,7 +122,7 @@
     <t>7</t>
   </si>
   <si>
-    <t>Sét, đôi chỗ kẹp cát pha, lẫn dăm sạn TT dẻo mềm</t>
+    <t>Sét, đôi chỗ kẹp cát pha, lẫn dăm sạn, TT dẻo mềm</t>
   </si>
   <si>
     <t xml:space="preserve">08:45
@@ -132,7 +132,7 @@
     <t>11</t>
   </si>
   <si>
-    <t>Sét xám vàng, nâu vàng xám xanh TT nửa cứng</t>
+    <t>Sét xám vàng, nâu vàng, xám xanh, TT nửa cứng</t>
   </si>
   <si>
     <t xml:space="preserve">09:15
@@ -149,7 +149,7 @@
     <t>13</t>
   </si>
   <si>
-    <t>Cát pha xám ghi, xám nâu, xám vàng TT dẻo</t>
+    <t>Cát pha, xám ghi, xám nâu, xám vàng, TT dẻo</t>
   </si>
   <si>
     <t xml:space="preserve">11:10
@@ -159,7 +159,7 @@
     <t>14</t>
   </si>
   <si>
-    <t>Cát thô vừa, xám vàng, xám xanh, xám nâu TT chặt</t>
+    <t>Cát thô vừa, xám vàng, xám xanh, TT chặt lẫn sỏi sạn, có chỗ là cát hạt nhỏ, bụi</t>
   </si>
   <si>
     <t xml:space="preserve">11:40
@@ -172,7 +172,7 @@
     <t>16</t>
   </si>
   <si>
-    <t>Sỏi xám vàng, nâu vàng, xám xanh TT rất chặt</t>
+    <t>Sỏi xám vàng, nâu vàng, xám xanh, TT rất chặt</t>
   </si>
   <si>
     <t xml:space="preserve">12:11
@@ -1186,7 +1186,7 @@
         <v>-2.18</v>
       </c>
       <c r="G12" s="9">
-        <v>-12.379999999999999</v>
+        <v>-12.38</v>
       </c>
       <c r="H12" s="9">
         <v>0.25</v>
@@ -1218,7 +1218,7 @@
         <v>36</v>
       </c>
       <c r="F13" s="12">
-        <v>-12.379999999999999</v>
+        <v>-12.38</v>
       </c>
       <c r="G13" s="12">
         <v>-17.58</v>
@@ -1256,7 +1256,7 @@
         <v>-17.58</v>
       </c>
       <c r="G14" s="15">
-        <v>-28.279999999999998</v>
+        <v>-28.28</v>
       </c>
       <c r="H14" s="15">
         <v>0.5</v>
@@ -1288,10 +1288,10 @@
         <v>41</v>
       </c>
       <c r="F15" s="18">
-        <v>-28.279999999999998</v>
+        <v>-28.28</v>
       </c>
       <c r="G15" s="18">
-        <v>-35.080000000000005</v>
+        <v>-35.08</v>
       </c>
       <c r="H15" s="18">
         <v>1.17</v>
@@ -1323,10 +1323,10 @@
         <v>44</v>
       </c>
       <c r="F16" s="21">
-        <v>-35.080000000000005</v>
+        <v>-35.08</v>
       </c>
       <c r="G16" s="21">
-        <v>-37.580000000000005</v>
+        <v>-37.58</v>
       </c>
       <c r="H16" s="21">
         <v>0.75</v>
@@ -1358,10 +1358,10 @@
         <v>47</v>
       </c>
       <c r="F17" s="25">
-        <v>-37.580000000000005</v>
+        <v>-37.58</v>
       </c>
       <c r="G17" s="25">
-        <v>-45.699999999999996</v>
+        <v>-45.7</v>
       </c>
       <c r="H17" s="25">
         <v>0.5</v>
@@ -1393,7 +1393,7 @@
         <v>51</v>
       </c>
       <c r="F18" s="28">
-        <v>-45.699999999999996</v>
+        <v>-45.7</v>
       </c>
       <c r="G18" s="28">
         <v>-50.22</v>
